--- a/Solutions/solution_models_H18.xlsx
+++ b/Solutions/solution_models_H18.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Thermolab-main\v_24_03_18\Solutions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Thermolab\v_25_05_12\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD1BDA4-89DA-4DB8-BF20-A7DB11B9C88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058CC3A1-7396-4FD6-B576-A62F18607C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="865" firstSheet="1" activeTab="2" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="865" firstSheet="18" activeTab="22" xr2:uid="{5AA2B440-0145-4F56-AB97-83AB8C8EBBCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Melt (Ab-An)" sheetId="50" r:id="rId1"/>
@@ -78,6 +78,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -8036,7 +8039,7 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -8051,7 +8054,7 @@
         <v>1</v>
       </c>
       <c r="L20">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M20">
         <v>1</v>
